--- a/praxe/Excel - 9.roč zadání.xlsx
+++ b/praxe/Excel - 9.roč zadání.xlsx
@@ -5,40 +5,37 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanSy\Desktop\praxe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanSy\Desktop\DELTA\praxe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70D1BD62-9957-4900-B0F1-95F1B5580F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C593E0F9-FDE8-48FC-BFFC-3F2041F4FE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vzorce" sheetId="15" r:id="rId1"/>
     <sheet name="Když" sheetId="22" r:id="rId2"/>
-    <sheet name="Pořadí_pravidla" sheetId="21" r:id="rId3"/>
-    <sheet name="Datumové" sheetId="20" r:id="rId4"/>
+    <sheet name="Datumové" sheetId="20" r:id="rId3"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
-    <definedName name="Data" localSheetId="3">#REF!</definedName>
+    <definedName name="Data" localSheetId="2">#REF!</definedName>
     <definedName name="Data">#REF!</definedName>
-    <definedName name="Data_nova" localSheetId="3">#REF!</definedName>
+    <definedName name="Data_nova" localSheetId="2">#REF!</definedName>
     <definedName name="Data_nova">#REF!</definedName>
-    <definedName name="DATA2" localSheetId="3">#REF!</definedName>
+    <definedName name="DATA2" localSheetId="2">#REF!</definedName>
     <definedName name="DATA2">#REF!</definedName>
-    <definedName name="hovno" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="hovno" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="hovno" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="hovno" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="hovno" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="jiná" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="jiná" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="jiná" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="jiná" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="jiná" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="Legenda">[1]Knihy!$A$9,[1]Knihy!$A$3:$A$9,[1]Knihy!$B$3:$G$3</definedName>
     <definedName name="MakroPokus">[2]!MakroPokus</definedName>
@@ -47,43 +44,37 @@
     <definedName name="mzdy_osoby">[3]Mzdy2!$A$4:$A$9</definedName>
     <definedName name="mzdy_součty">[3]Mzdy2!$B$10:$I$10</definedName>
     <definedName name="mzdy_vzorce">'[1]Mzdy '!$F$4:$J$10,'[1]Mzdy '!$B$10:$C$10,'[1]Mzdy '!$D$10,'[1]Mzdy '!$E$10,'[1]Mzdy '!$E$4:$E$9</definedName>
-    <definedName name="nápoje" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="nápoje" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nápoje" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="nápoje" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nápoje" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="nevím" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="nevím" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nevím" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="nevím" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nevím" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="nic" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="nic" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nic" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="nic" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="nic" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="ooo">[2]List2!$A$18:$B$22,[2]List2!$F$17:$G$21</definedName>
     <definedName name="počet_návštěvníků">#REF!</definedName>
-    <definedName name="podmínka" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="podmínka" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="podmínka" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="podmínka" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="podmínka" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="Pojistné">[3]Mzdy3!$J$1</definedName>
     <definedName name="Prémie">[3]Mzdy2!$C$4:$C$9</definedName>
     <definedName name="Příplatek">[1]Mzdy2!#REF!</definedName>
     <definedName name="sazba_daně">'[4]závislost vzorců, pojm. oblasti'!$G$2</definedName>
-    <definedName name="sdfv" localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="sdfv" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="sdfv" localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="sdfv" localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="sdfv" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="Seznam1">#REF!</definedName>
     <definedName name="ssss">#REF!</definedName>
     <definedName name="Titul_a_součty">[1]Trafika!$A$3:$J$3,[1]Trafika!$A$23:$J$23</definedName>
     <definedName name="Tituly">[3]Trafika!$A$4:$A$22</definedName>
-    <definedName name="ÚČAST" localSheetId="3">#REF!</definedName>
+    <definedName name="ÚČAST" localSheetId="2">#REF!</definedName>
     <definedName name="ÚČAST">#REF!</definedName>
     <definedName name="vstupné">#REF!</definedName>
     <definedName name="Výpočty">[1]Knihy!$G$4:$G$9,[1]Knihy!$B$9:$F$9</definedName>
-    <definedName name="wrn.Pokusná." localSheetId="3" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
+    <definedName name="wrn.Pokusná." localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="wrn.Pokusná." localSheetId="1" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
-    <definedName name="wrn.Pokusná." localSheetId="2" hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="wrn.Pokusná." hidden="1">{"Normálně",#N/A,FALSE,"Knihy";#N/A,#N/A,FALSE,"Směny3"}</definedName>
     <definedName name="xxx">[2]List2!$A$2:$B$5,[2]List2!$D$2:$F$5</definedName>
     <definedName name="zdroj">INDIRECT("Data!$A1:$H"&amp;65536-COUNTBLANK('[5]kontingenční tabulka '!$A:$A))</definedName>
@@ -138,48 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{2FD6E7C5-8798-45DD-92A9-0AFA38DB94EE}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">použijte fci POWER
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{02B3E0D7-6D76-4B8A-8457-A058764732FD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>použijte znak stříšky ^</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{2A3D3FFE-02A9-4856-A8D1-1E029FBBD94B}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{2A3D3FFE-02A9-4856-A8D1-1E029FBBD94B}">
       <text>
         <r>
           <rPr>
@@ -205,38 +155,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{F3CD93BF-EF6A-4278-A597-C45764D42CCB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>Votavová Gabriela:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">
-jedná se o pořadí konkrétního čísla v řadě čísel x v řádku 19</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>datum</t>
   </si>
@@ -280,12 +204,6 @@
     <t xml:space="preserve">Druhá mocnina x </t>
   </si>
   <si>
-    <t>Druhá mocnina x</t>
-  </si>
-  <si>
-    <t>Třetí odmocnina x</t>
-  </si>
-  <si>
     <t>Druhá odmocnina x</t>
   </si>
   <si>
@@ -304,97 +222,13 @@
     <t>Čtvrtá odmocnina y</t>
   </si>
   <si>
-    <t>Dopočítejte hodnoty "y" a "x" dle daných vzorců a známých funkcí, více v komentářích</t>
-  </si>
-  <si>
-    <t>Pořadí</t>
-  </si>
-  <si>
-    <t>Vynásob čísla x pomocí funkce</t>
-  </si>
-  <si>
-    <t>Vynásob čísla x pomocí vzorce</t>
-  </si>
-  <si>
-    <t>Sečti čísla x pomocí funkce</t>
-  </si>
-  <si>
-    <t>Sečti čísla x pomocí vzorce</t>
-  </si>
-  <si>
-    <t>Sečti čísla x větší než 4</t>
-  </si>
-  <si>
-    <t>Zadej pořadí čísla x vzestupně</t>
-  </si>
-  <si>
     <t>Den v týdnu (číslo dne)</t>
-  </si>
-  <si>
-    <t>Stáří  =YEARFRAC</t>
-  </si>
-  <si>
-    <t>Počet dnů ke dnešku</t>
   </si>
   <si>
     <t>den týdne</t>
   </si>
   <si>
-    <t>datum dlouhý formát složený (D14:F14)</t>
-  </si>
-  <si>
     <t>ÚKOL: doplňte správné funkce do modrých polí a upravte tak, aby byla všechna pole dobře čitelná</t>
-  </si>
-  <si>
-    <t>ÚKOL 1-3: Dopočítej prázdné buňky v tabulce pomocí vhodné funkce pořadí a funkce zaokrouhlení. Zadej ověřovací pravidla a statistické funkce.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4" tint="-0.499984740745262"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t>Zadej vzestupné řazení:</t>
-    </r>
-  </si>
-  <si>
-    <t>Zaokrouhlení času na celé číslo</t>
-  </si>
-  <si>
-    <t>Běžci</t>
-  </si>
-  <si>
-    <t>Čas</t>
-  </si>
-  <si>
-    <t>Průměrné pořadí</t>
-  </si>
-  <si>
-    <r>
-      <t>ÚKOL:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve"> Vypište do buňky B6 správné kritérium pomocí vnořené funkce Když, tak aby odpovídalo zadaným bodům v buňce E3. </t>
-    </r>
   </si>
   <si>
     <t>Výsledný počet bodů</t>
@@ -412,109 +246,42 @@
     <t>a více</t>
   </si>
   <si>
-    <t>bohužel, ale oprava je možná</t>
-  </si>
-  <si>
     <t>y = 5x - 2</t>
-  </si>
-  <si>
-    <t>nepovedlo se</t>
   </si>
   <si>
     <t>paráda</t>
   </si>
   <si>
-    <t>Ilona</t>
-  </si>
-  <si>
-    <t>Klára</t>
-  </si>
-  <si>
-    <t>Darina</t>
-  </si>
-  <si>
-    <t>Leopold</t>
-  </si>
-  <si>
-    <t>Anděla</t>
-  </si>
-  <si>
-    <t>Evelína</t>
-  </si>
-  <si>
-    <t>Antonín</t>
-  </si>
-  <si>
-    <t>Běh na 800 m</t>
+    <t>neprošel</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">2, </t>
+      <t>ÚKOL:</t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.499984740745262"/>
-        <rFont val="Arial CE"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
-      <t>Do buňky H9 zadej ověřovací pravidlo tak, aby bylo možné vložit jen desetinná čísla větší než 5,55. Zadej vhodnou Zprávu při zadávání a Chybové hlášení. Buňku s pravidlem zvýrazni.</t>
+      <t xml:space="preserve"> Vypište do buňky B6 správné kritérium pomocí  funkce Když, tak aby odpovídalo zadaným bodům v buňce E3. </t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">3, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4" tint="-0.499984740745262"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">Použij vhodnou funkci na zjištění dat z tabulky:  kolikrát je zobrazeno číslo 4,66 a za </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4" tint="-0.499984740745262"/>
-        <rFont val="Arial CE"/>
-        <charset val="238"/>
-      </rPr>
-      <t>kolik je součet čísel větších než 4,80. Hodnoty zadej do nové tabulky pod uvedenou tabuku a vhodně uprav, tak aby bylo jasné co zobrazují.</t>
-    </r>
+    <t>Dopočítejte hodnoty "y" a "x" dle daných vzorců a známých funkcí POWER a ODMOCNINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,57 +425,11 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF002060"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial CE"/>
-      <charset val="238"/>
     </font>
     <font>
       <b/>
@@ -754,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,12 +496,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -792,7 +507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -915,57 +630,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -976,15 +640,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1000,56 +655,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1076,30 +681,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1162,7 +743,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyFont="1"/>
@@ -1194,172 +775,96 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="17" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="22" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Měna 2" xfId="5" xr:uid="{8A5E79A9-06AD-4156-A0A0-BC178852EE71}"/>
     <cellStyle name="Měna 2 3" xfId="10" xr:uid="{331F6D55-8EF3-44F0-9C7B-C16243EB541F}"/>
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normální 2" xfId="1" xr:uid="{E03A5351-5B77-47BE-B652-A5158947DEE2}"/>
     <cellStyle name="Normální 2 2" xfId="8" xr:uid="{DB32CE5B-670B-4EF9-84CE-8B26EE9F70AC}"/>
     <cellStyle name="Normální 3" xfId="4" xr:uid="{5DF7EFB6-3A3E-4F55-8D79-EEFBF0464A2B}"/>
@@ -16710,7 +16215,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16739,46 +16244,46 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="48">
+      <c r="B3" s="36">
         <v>-7</v>
       </c>
-      <c r="C3" s="49">
+      <c r="C3" s="37">
         <v>-4</v>
       </c>
-      <c r="D3" s="49">
+      <c r="D3" s="37">
         <v>-2</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="37">
         <v>-5</v>
       </c>
-      <c r="F3" s="49">
+      <c r="F3" s="37">
         <v>-1</v>
       </c>
-      <c r="G3" s="49">
+      <c r="G3" s="37">
         <v>0</v>
       </c>
-      <c r="H3" s="49">
+      <c r="H3" s="37">
         <v>1</v>
       </c>
-      <c r="I3" s="49">
+      <c r="I3" s="37">
         <v>8</v>
       </c>
-      <c r="J3" s="49">
+      <c r="J3" s="37">
         <v>2</v>
       </c>
-      <c r="K3" s="48">
+      <c r="K3" s="36">
         <v>6</v>
       </c>
-      <c r="L3" s="49">
+      <c r="L3" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
@@ -16829,48 +16334,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="8"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
@@ -16887,10 +16360,10 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46" t="s">
-        <v>17</v>
+      <c r="A11" s="34" t="s">
+        <v>15</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="34">
         <v>4</v>
       </c>
       <c r="C11" s="3"/>
@@ -16905,10 +16378,10 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46" t="s">
-        <v>18</v>
+      <c r="A12" s="34" t="s">
+        <v>16</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="34">
         <v>2</v>
       </c>
       <c r="C12" s="3"/>
@@ -16923,46 +16396,46 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="36">
         <v>-7</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="37">
         <v>-4</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="37">
         <v>-2</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="37">
         <v>-5</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="37">
         <v>-1</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="37">
         <v>0</v>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="37">
         <v>1</v>
       </c>
-      <c r="I13" s="49">
+      <c r="I13" s="37">
         <v>8</v>
       </c>
-      <c r="J13" s="49">
+      <c r="J13" s="37">
         <v>2</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="36">
         <v>6</v>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -16978,7 +16451,7 @@
     </row>
     <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -16994,108 +16467,53 @@
     </row>
     <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="52">
-        <v>2</v>
-      </c>
-      <c r="C19" s="48">
-        <v>7</v>
-      </c>
-      <c r="D19" s="49">
-        <v>5</v>
-      </c>
-      <c r="E19" s="49">
-        <v>1</v>
-      </c>
-      <c r="F19" s="53">
-        <v>4</v>
-      </c>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="58"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
     </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="64"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="58"/>
     </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="65"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="58"/>
     </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="85"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="58"/>
     </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="58"/>
     </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="58"/>
     </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="58"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
+  <mergeCells count="1">
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17112,78 +16530,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>42</v>
+      <c r="A1" s="27" t="s">
+        <v>31</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="69" t="s">
-        <v>43</v>
+      <c r="B3" s="47" t="s">
+        <v>23</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="54"/>
-      <c r="G3" s="71" t="s">
-        <v>44</v>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="39"/>
+      <c r="G3" s="49" t="s">
+        <v>24</v>
       </c>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="39">
+      <c r="G4" s="29">
         <v>0</v>
       </c>
-      <c r="H4" s="40" t="s">
-        <v>45</v>
+      <c r="H4" s="30" t="s">
+        <v>25</v>
       </c>
-      <c r="I4" s="40">
-        <v>45</v>
+      <c r="I4" s="30">
+        <v>70</v>
       </c>
-      <c r="J4" s="41" t="s">
-        <v>50</v>
+      <c r="J4" s="31" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="74" t="s">
-        <v>46</v>
+      <c r="B5" s="52" t="s">
+        <v>26</v>
       </c>
-      <c r="C5" s="75"/>
-      <c r="G5" s="42">
-        <v>46</v>
+      <c r="C5" s="53"/>
+      <c r="G5" s="32">
+        <v>71</v>
       </c>
-      <c r="H5" s="35" t="s">
-        <v>45</v>
+      <c r="H5" s="54" t="s">
+        <v>27</v>
       </c>
-      <c r="I5" s="35">
-        <v>70</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>48</v>
+      <c r="I5" s="54"/>
+      <c r="J5" s="33" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="71"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="73"/>
-      <c r="G6" s="44">
-        <v>71</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="76"/>
-      <c r="J6" s="45" t="s">
-        <v>51</v>
-      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -17191,7 +16597,7 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -17199,283 +16605,45 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFEF52D-2A7A-4B81-A1BE-F0C565899654}">
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-    </row>
-    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="P4" s="32"/>
-    </row>
-    <row r="5" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="78" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="81" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-    </row>
-    <row r="6" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="82"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="35">
-        <v>5.07</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="35">
-        <v>4.87</v>
-      </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="35">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="35">
-        <v>5.32</v>
-      </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="35">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-    </row>
-    <row r="12" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="35">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="P12" s="32"/>
-    </row>
-    <row r="13" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="35">
-        <v>4.87</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="H13" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-    </row>
-    <row r="14" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-    </row>
-    <row r="15" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-    </row>
-    <row r="16" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-    </row>
-    <row r="17" spans="8:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-    </row>
-    <row r="18" spans="8:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-    </row>
-    <row r="19" spans="8:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="H3:L7"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="H13:L19"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{322CBB04-82B3-48AE-9C3A-F7FE89F4DDC6}">
-      <formula1>20.6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A69CBA-3EAE-413B-AE70-7ED0390DE697}">
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="11" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="11" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="11" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>30</v>
+      <c r="B1" s="40" t="s">
+        <v>20</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="57" t="s">
-        <v>31</v>
+      <c r="F1" s="56"/>
+      <c r="G1" s="55"/>
+      <c r="I1" s="46" t="s">
+        <v>22</v>
       </c>
-      <c r="G1" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="84" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
@@ -17485,13 +16653,13 @@
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="55"/>
       <c r="H2"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
@@ -17501,13 +16669,13 @@
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="55"/>
       <c r="H3"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
@@ -17517,12 +16685,12 @@
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="55"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
@@ -17532,8 +16700,8 @@
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="55"/>
       <c r="H5"/>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
@@ -17544,8 +16712,8 @@
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="55"/>
       <c r="H6"/>
     </row>
     <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.25">
@@ -17556,8 +16724,8 @@
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="55"/>
       <c r="H7"/>
     </row>
     <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.25">
@@ -17568,8 +16736,8 @@
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="55"/>
       <c r="H8"/>
     </row>
     <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.25">
@@ -17580,8 +16748,8 @@
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="55"/>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -17597,8 +16765,8 @@
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="55"/>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -17634,26 +16802,24 @@
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:13" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="59" t="s">
-        <v>33</v>
+      <c r="C13" s="42" t="s">
+        <v>21</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="60" t="s">
-        <v>34</v>
-      </c>
+      <c r="G13" s="56"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -17665,12 +16831,12 @@
       <c r="A14" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="27"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="28"/>
+      <c r="G14" s="56"/>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
@@ -17699,16 +16865,16 @@
       <c r="B17" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="43" t="s">
         <v>9</v>
       </c>
     </row>
@@ -17716,7 +16882,7 @@
       <c r="A18" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="16"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -17790,15 +16956,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010019746E8B3FF2B2428A148D03C368DE4A" ma:contentTypeVersion="13" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="9d94cbd9914ef4824ad723384dcde04a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ea85f2e0-d32a-4312-be8a-c00aff2510cf" xmlns:ns4="c52afa11-cb76-49c2-a807-b2856752eead" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f78cee60d32ecf43d3cd1d8f83bcfaea" ns3:_="" ns4:_="">
     <xsd:import namespace="ea85f2e0-d32a-4312-be8a-c00aff2510cf"/>
@@ -18021,6 +17178,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1E5C1E-19BF-468D-B0B2-61003722B554}">
   <ds:schemaRefs>
@@ -18039,14 +17205,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2332F859-5A93-4362-A0AD-5F1B2CA9AE12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABB90D82-CE66-4F15-BA28-0C76387BD7AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18063,4 +17221,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2332F859-5A93-4362-A0AD-5F1B2CA9AE12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/praxe/Excel - 9.roč zadání.xlsx
+++ b/praxe/Excel - 9.roč zadání.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanSy\Desktop\DELTA\praxe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanSy\Desktop\DELTA PROJEKTY\DELTA\praxe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C593E0F9-FDE8-48FC-BFFC-3F2041F4FE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35EF0E0-16B6-43D9-A1C4-9159C13AD24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vzorce" sheetId="15" r:id="rId1"/>
@@ -281,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,20 +397,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF92D050"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -743,7 +729,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyFont="1"/>
@@ -767,9 +753,7 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -779,21 +763,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -811,7 +795,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -822,28 +806,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="8" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="22" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -855,16 +838,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="22" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Měna 2" xfId="5" xr:uid="{8A5E79A9-06AD-4156-A0A0-BC178852EE71}"/>
     <cellStyle name="Měna 2 3" xfId="10" xr:uid="{331F6D55-8EF3-44F0-9C7B-C16243EB541F}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Normální 2" xfId="1" xr:uid="{E03A5351-5B77-47BE-B652-A5158947DEE2}"/>
     <cellStyle name="Normální 2 2" xfId="8" xr:uid="{DB32CE5B-670B-4EF9-84CE-8B26EE9F70AC}"/>
     <cellStyle name="Normální 3" xfId="4" xr:uid="{5DF7EFB6-3A3E-4F55-8D79-EEFBF0464A2B}"/>
@@ -16244,40 +16222,40 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="34">
         <v>-7</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="35">
         <v>-4</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="35">
         <v>-2</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="35">
         <v>-5</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="35">
         <v>-1</v>
       </c>
-      <c r="G3" s="37">
+      <c r="G3" s="35">
         <v>0</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="35">
         <v>1</v>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="35">
         <v>8</v>
       </c>
-      <c r="J3" s="37">
+      <c r="J3" s="35">
         <v>2</v>
       </c>
-      <c r="K3" s="36">
+      <c r="K3" s="34">
         <v>6</v>
       </c>
-      <c r="L3" s="37">
+      <c r="L3" s="35">
         <v>4</v>
       </c>
     </row>
@@ -16317,33 +16295,99 @@
       <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="B6" s="8">
+        <f>POWER(B3,2)</f>
+        <v>49</v>
+      </c>
+      <c r="C6" s="8">
+        <f t="shared" ref="C6:L6" si="0">POWER(C3,2)</f>
+        <v>16</v>
+      </c>
+      <c r="D6" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="L6" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
+      <c r="B7" s="8" t="e">
+        <f>POWER(B3,1/2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C7" s="8" t="e">
+        <f t="shared" ref="C7:L7" si="1">POWER(C3,1/2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D7" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E7" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="F7" s="8" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="1"/>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="1"/>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="1"/>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
@@ -16360,10 +16404,10 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="32">
         <v>4</v>
       </c>
       <c r="C11" s="3"/>
@@ -16378,10 +16422,10 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="32">
         <v>2</v>
       </c>
       <c r="C12" s="3"/>
@@ -16396,40 +16440,40 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="34">
         <v>-7</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="35">
         <v>-4</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="35">
         <v>-2</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="35">
         <v>-5</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="35">
         <v>-1</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="35">
         <v>0</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="35">
         <v>1</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="35">
         <v>8</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="35">
         <v>2</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K13" s="34">
         <v>6</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="35">
         <v>4</v>
       </c>
     </row>
@@ -16470,46 +16514,46 @@
         <v>19</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="58"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="58"/>
+      <c r="A20" s="45"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="58"/>
+      <c r="A21" s="45"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="58"/>
+      <c r="A22" s="45"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="58"/>
+      <c r="A23" s="45"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="58"/>
+      <c r="A24" s="45"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16530,66 +16574,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="39"/>
-      <c r="G3" s="49" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="37">
+        <v>90</v>
+      </c>
+      <c r="G3" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="29">
+      <c r="G4" s="27">
         <v>0</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="28">
         <v>70</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="G5" s="32">
+      <c r="C5" s="54"/>
+      <c r="G5" s="30">
         <v>71</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="54"/>
-      <c r="J5" s="33" t="s">
+      <c r="I5" s="55"/>
+      <c r="J5" s="31" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="51"/>
+      <c r="B6" s="50" t="str">
+        <f>IF(E3&gt;71,"prošel", "neprošel")</f>
+        <v>prošel</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16621,23 +16670,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="56"/>
-      <c r="G1" s="55"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="42"/>
       <c r="I1" s="46" t="s">
         <v>22</v>
       </c>
@@ -16649,12 +16698,24 @@
       <c r="A2" s="15">
         <v>44747</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="55"/>
+      <c r="B2" s="14">
+        <f>WEEKDAY(A2)</f>
+        <v>3</v>
+      </c>
+      <c r="C2" s="14">
+        <f>YEAR(A2)</f>
+        <v>2022</v>
+      </c>
+      <c r="D2" s="14">
+        <f>MONTH(A2)</f>
+        <v>7</v>
+      </c>
+      <c r="E2" s="14">
+        <f>DAY(A2)</f>
+        <v>5</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="42"/>
       <c r="H2"/>
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
@@ -16665,12 +16726,24 @@
       <c r="A3" s="15">
         <v>26760</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="55"/>
+      <c r="B3" s="14">
+        <f t="shared" ref="B3:B10" si="0">WEEKDAY(A3)</f>
+        <v>6</v>
+      </c>
+      <c r="C3" s="14">
+        <f t="shared" ref="C3:C10" si="1">YEAR(A3)</f>
+        <v>1973</v>
+      </c>
+      <c r="D3" s="14">
+        <f t="shared" ref="D3:D10" si="2">MONTH(A3)</f>
+        <v>4</v>
+      </c>
+      <c r="E3" s="14">
+        <f t="shared" ref="E3:E10" si="3">DAY(A3)</f>
+        <v>6</v>
+      </c>
+      <c r="F3" s="43"/>
+      <c r="G3" s="42"/>
       <c r="H3"/>
       <c r="I3" s="46"/>
       <c r="J3" s="46"/>
@@ -16681,12 +16754,24 @@
       <c r="A4" s="15">
         <v>35646</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="55"/>
+      <c r="B4" s="14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C4" s="14">
+        <f t="shared" si="1"/>
+        <v>1997</v>
+      </c>
+      <c r="D4" s="14">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E4" s="14">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F4" s="43"/>
+      <c r="G4" s="42"/>
       <c r="I4" s="46"/>
       <c r="J4" s="46"/>
       <c r="K4" s="46"/>
@@ -16696,60 +16781,120 @@
       <c r="A5" s="15">
         <v>19059</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="55"/>
+      <c r="B5" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C5" s="14">
+        <f t="shared" si="1"/>
+        <v>1952</v>
+      </c>
+      <c r="D5" s="14">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="14">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F5" s="43"/>
+      <c r="G5" s="42"/>
       <c r="H5"/>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <v>42718</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="55"/>
+      <c r="B6" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C6" s="14">
+        <f t="shared" si="1"/>
+        <v>2016</v>
+      </c>
+      <c r="D6" s="14">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="E6" s="14">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="42"/>
       <c r="H6"/>
     </row>
     <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>45243</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="55"/>
+      <c r="B7" s="14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C7" s="14">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="D7" s="14">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="E7" s="14">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="F7" s="43"/>
+      <c r="G7" s="42"/>
       <c r="H7"/>
     </row>
     <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>44472</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="55"/>
+      <c r="B8" s="14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C8" s="14">
+        <f t="shared" si="1"/>
+        <v>2021</v>
+      </c>
+      <c r="D8" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F8" s="43"/>
+      <c r="G8" s="42"/>
       <c r="H8"/>
     </row>
     <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>37787</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="55"/>
+      <c r="B9" s="14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
+        <f t="shared" si="1"/>
+        <v>2003</v>
+      </c>
+      <c r="D9" s="14">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E9" s="14">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="42"/>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -16761,12 +16906,24 @@
       <c r="A10" s="15">
         <v>38631</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="55"/>
+      <c r="B10" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C10" s="14">
+        <f t="shared" si="1"/>
+        <v>2005</v>
+      </c>
+      <c r="D10" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E10" s="14">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
@@ -16776,7 +16933,7 @@
     </row>
     <row r="11" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="19"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -16803,23 +16960,23 @@
       <c r="M12"/>
     </row>
     <row r="13" spans="1:13" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="56"/>
+      <c r="G13" s="43"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -16828,15 +16985,18 @@
       <c r="M13"/>
     </row>
     <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="26"/>
+      <c r="B14" s="24">
+        <f ca="1">TODAY()</f>
+        <v>46162</v>
+      </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="56"/>
+      <c r="G14" s="43"/>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
@@ -16854,35 +17014,38 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
-      <c r="B16" s="23"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="41" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="57"/>
+      <c r="B18" s="44">
+        <f ca="1">NOW()</f>
+        <v>46162.485583217589</v>
+      </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -16890,11 +17053,11 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
@@ -16950,9 +17113,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17179,27 +17345,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1E5C1E-19BF-468D-B0B2-61003722B554}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2332F859-5A93-4362-A0AD-5F1B2CA9AE12}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ea85f2e0-d32a-4312-be8a-c00aff2510cf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c52afa11-cb76-49c2-a807-b2856752eead"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17224,9 +17378,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2332F859-5A93-4362-A0AD-5F1B2CA9AE12}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1E5C1E-19BF-468D-B0B2-61003722B554}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ea85f2e0-d32a-4312-be8a-c00aff2510cf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c52afa11-cb76-49c2-a807-b2856752eead"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>